--- a/PO_TBD_20260612.xlsx
+++ b/PO_TBD_20260612.xlsx
@@ -2550,7 +2550,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-12 11:37</t>
+          <t>Generated: 2026-06-12 11:45</t>
         </is>
       </c>
     </row>
